--- a/artfynd/A 63588-2021 artfynd.xlsx
+++ b/artfynd/A 63588-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63588-2021 artfynd.xlsx
+++ b/artfynd/A 63588-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99802068</v>
+        <v>103307099</v>
       </c>
       <c r="B2" t="n">
-        <v>89777</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6040186</v>
+        <v>658</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>652405.8071648835</v>
+        <v>652546</v>
       </c>
       <c r="R2" t="n">
-        <v>7182935.78986345</v>
+        <v>7182845</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Carl Jansson, Emil Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -804,12 +794,7 @@
         <v>99802067</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>652408.0087384946</v>
+        <v>652408</v>
       </c>
       <c r="R3" t="n">
-        <v>7182934.617445469</v>
+        <v>7182935</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +859,9 @@
           <t>2022-04-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99802054</v>
+        <v>103307087</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -972,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>652641.3725686073</v>
+        <v>652648</v>
       </c>
       <c r="R4" t="n">
-        <v>7182903.63794224</v>
+        <v>7182870</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,22 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,21 +988,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1052,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Carl Jansson, Emil Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1063,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99802065</v>
+        <v>103307090</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1103,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652407.9409682426</v>
+        <v>652584</v>
       </c>
       <c r="R5" t="n">
-        <v>7182859.7256604</v>
+        <v>7182865</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,22 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,21 +1089,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1183,7 +1098,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Carl Jansson, Emil Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1194,15 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99802064</v>
+        <v>103307101</v>
       </c>
       <c r="B6" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1234,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652407.9841511692</v>
+        <v>652556</v>
       </c>
       <c r="R6" t="n">
-        <v>7182858.871967146</v>
+        <v>7182843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1264,22 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,21 +1190,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1314,7 +1199,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Carl Jansson, Emil Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1325,37 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103307092</v>
+        <v>103307089</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1365,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>652539.8903096291</v>
+        <v>652610</v>
       </c>
       <c r="R7" t="n">
-        <v>7182868.542736805</v>
+        <v>7182862</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1398,19 +1278,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1441,19 +1311,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103307100</v>
+        <v>103307092</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1481,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>652556.144983532</v>
+        <v>652540</v>
       </c>
       <c r="R8" t="n">
-        <v>7182843.689223171</v>
+        <v>7182868</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1514,19 +1379,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,16 +1415,11 @@
         <v>103307095</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1597,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>652495.1339246557</v>
+        <v>652495</v>
       </c>
       <c r="R9" t="n">
-        <v>7182847.019835757</v>
+        <v>7182847</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1630,19 +1480,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,15 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103307089</v>
+        <v>103307100</v>
       </c>
       <c r="B10" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,21 +1524,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1713,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>652610.0920132224</v>
+        <v>652556</v>
       </c>
       <c r="R10" t="n">
-        <v>7182861.399177596</v>
+        <v>7182844</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,19 +1581,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,37 +1614,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103307090</v>
+        <v>99802054</v>
       </c>
       <c r="B11" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1829,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>652583.7630020322</v>
+        <v>652641</v>
       </c>
       <c r="R11" t="n">
-        <v>7182865.201002063</v>
+        <v>7182904</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1859,22 +1679,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1885,6 +1695,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1894,7 +1719,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1905,37 +1730,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103307101</v>
+        <v>99802065</v>
       </c>
       <c r="B12" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1945,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>652556.1882084066</v>
+        <v>652408</v>
       </c>
       <c r="R12" t="n">
-        <v>7182842.835524919</v>
+        <v>7182860</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,22 +1795,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,6 +1811,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2010,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2021,37 +1846,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103307099</v>
+        <v>103307094</v>
       </c>
       <c r="B13" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2061,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>652546.2505689061</v>
+        <v>652526</v>
       </c>
       <c r="R13" t="n">
-        <v>7182844.472090066</v>
+        <v>7182863</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2094,19 +1914,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2152,15 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103307094</v>
+        <v>99802064</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2192,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>652526.0248038825</v>
+        <v>652408</v>
       </c>
       <c r="R14" t="n">
-        <v>7182863.133453391</v>
+        <v>7182859</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2222,22 +2027,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2272,7 +2067,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2283,15 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103307087</v>
+        <v>99802068</v>
       </c>
       <c r="B15" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,21 +2089,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>6040186</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2323,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>652647.8036098615</v>
+        <v>652406</v>
       </c>
       <c r="R15" t="n">
-        <v>7182869.728659357</v>
+        <v>7182936</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2353,22 +2143,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2379,6 +2159,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2388,7 +2183,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 63588-2021 artfynd.xlsx
+++ b/artfynd/A 63588-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307099</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99802067</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307087</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307090</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307101</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307089</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307092</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307095</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307100</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99802054</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1843,6 +1898,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99802065</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1959,6 +2019,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307094</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2075,6 +2140,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99802064</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2191,8 +2261,29 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99802068</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>